--- a/data_src/Base_emprendimientos.xlsx
+++ b/data_src/Base_emprendimientos.xlsx
@@ -1,38 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tzafon-my.sharepoint.com/personal/msagarraga_construirsa_com/Documents/Manuel Sagarraga/Planificación/Tableros/Loteos y edificios/Formato Nuevo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{6EF89FA6-8714-4E0D-BE98-228CB08B1897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE98924-CEEE-460D-BC91-8621F0C07E0A}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{6EF89FA6-8714-4E0D-BE98-228CB08B1897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF51B93-58BB-4FD8-A89A-CB4EAF68816F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{186321B6-1986-4846-B637-EA981D8166FA}"/>
   </bookViews>
   <sheets>
     <sheet name="ID-Pipeline" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="130">
   <si>
     <t>Id Pipeline</t>
   </si>
   <si>
+    <t>Tiene Gas</t>
+  </si>
+  <si>
+    <t>Porcentaje avance obra Gas</t>
+  </si>
+  <si>
+    <t>Tiene Agua</t>
+  </si>
+  <si>
+    <t>Porcentaje avance obra Agua</t>
+  </si>
+  <si>
+    <t>Tiene Cloacas</t>
+  </si>
+  <si>
+    <t>Porcentaje avance obra Cloacas</t>
+  </si>
+  <si>
+    <t>Tiene Electricidad e Iluminación</t>
+  </si>
+  <si>
+    <t>Porcentaje avance obra Electricidad e Iluminación</t>
+  </si>
+  <si>
+    <t>Tiene Espacios Verdes</t>
+  </si>
+  <si>
+    <t>Porcentaje avance obra Espacios Verdes</t>
+  </si>
+  <si>
+    <t>Tiene red vial</t>
+  </si>
+  <si>
+    <t>Porcentaje avance obra Red Vial</t>
+  </si>
+  <si>
     <t xml:space="preserve">VCC - Terreno 5Ha </t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
     <t>VCC - Subdivisión Sur - Fortaleza &amp; Laurel - Sector Oeste</t>
   </si>
   <si>
@@ -231,22 +284,16 @@
     <t>N67 - Nuevo Guaymallen - B° El Equipo</t>
   </si>
   <si>
+    <t>N65 - Meglioli</t>
+  </si>
+  <si>
     <t>N64 - C. H. Rodríguez II</t>
   </si>
   <si>
     <t>N63 - Crouzeilles</t>
   </si>
   <si>
-    <t>N62 - Carrodilla Sector Sur - Etapa II M</t>
-  </si>
-  <si>
-    <t>N62 - Carrodilla Sector Sur - Etapa II</t>
-  </si>
-  <si>
-    <t>N62 - Carrodilla Sector Sur - Etapa I</t>
-  </si>
-  <si>
-    <t>N62 - Carrodilla Sector Norte</t>
+    <t>N62 - Carrodilla Sector Sur</t>
   </si>
   <si>
     <t>N61 - Leguizamón - III</t>
@@ -379,51 +426,6 @@
   </si>
   <si>
     <t>VCC - La Amistad</t>
-  </si>
-  <si>
-    <t>Tiene Gas</t>
-  </si>
-  <si>
-    <t>Porcentaje avance obra Gas</t>
-  </si>
-  <si>
-    <t>Tiene Agua</t>
-  </si>
-  <si>
-    <t>Porcentaje avance obra Agua</t>
-  </si>
-  <si>
-    <t>Tiene Cloacas</t>
-  </si>
-  <si>
-    <t>Porcentaje avance obra Cloacas</t>
-  </si>
-  <si>
-    <t>Tiene Electricidad e Iluminación</t>
-  </si>
-  <si>
-    <t>Porcentaje avance obra Electricidad e Iluminación</t>
-  </si>
-  <si>
-    <t>Tiene Espacios Verdes</t>
-  </si>
-  <si>
-    <t>Porcentaje avance obra Espacios Verdes</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Tiene red vial</t>
-  </si>
-  <si>
-    <t>Porcentaje avance obra Red Vial</t>
-  </si>
-  <si>
-    <t>N65 - Meglioli</t>
   </si>
 </sst>
 </file>
@@ -1060,8 +1062,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C11D5BB-6E7F-495A-8630-57EEE9ED707D}" name="Tabla33" displayName="Tabla33" ref="B2:N120" totalsRowShown="0">
-  <autoFilter ref="B2:N120" xr:uid="{5EF82ADA-92C0-4046-9873-D007DF2DF3F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C11D5BB-6E7F-495A-8630-57EEE9ED707D}" name="Tabla33" displayName="Tabla33" ref="B2:N117" totalsRowShown="0">
+  <autoFilter ref="B2:N117" xr:uid="{5EF82ADA-92C0-4046-9873-D007DF2DF3F2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{CAFB1AD4-2693-485F-BE91-7365DB5C2907}" name="Id Pipeline" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{F9E3AE6C-CEBB-450A-8EC4-D886522B623F}" name="Tiene Gas" dataDxfId="11"/>
@@ -1082,7 +1084,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1379,18 +1381,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9896A896-5C32-4D49-B765-A86BFC70A98B}">
   <dimension ref="B2:Q120"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.9"/>
   <cols>
     <col min="2" max="2" width="64.5" customWidth="1"/>
-    <col min="4" max="4" width="28.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.69921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.69921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -1398,1503 +1400,1503 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="J2" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="L2" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="M2" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="N2" t="s">
-        <v>131</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="2:17">
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L3" s="11"/>
       <c r="M3" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N3" s="11"/>
       <c r="Q3" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N4" s="12"/>
       <c r="Q4" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:17">
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="2:17">
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="2:17">
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="2:14">
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="2:14">
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="2:14" ht="15" customHeight="1">
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J20" s="12"/>
       <c r="K20" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="2:14">
       <c r="B21" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="2:14">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="2:14">
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J25" s="12"/>
       <c r="K25" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="2:14">
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J26" s="12"/>
       <c r="K26" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="2:14">
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J27" s="12"/>
       <c r="K27" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="2:14">
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="2:14">
       <c r="B29" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="2:14">
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="2:14">
       <c r="B31" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="2:14">
       <c r="B32" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J32" s="12"/>
       <c r="K32" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L32" s="12"/>
       <c r="M32" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J33" s="12"/>
       <c r="K33" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12"/>
       <c r="M33" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J34" s="12"/>
       <c r="K34" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L34" s="12"/>
       <c r="M34" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="2:14">
       <c r="B35" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J35" s="12"/>
       <c r="K35" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L35" s="12"/>
       <c r="M35" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="2:14">
       <c r="B36" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J36" s="12"/>
       <c r="K36" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12"/>
       <c r="M36" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="2:14">
       <c r="B37" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J37" s="12"/>
       <c r="K37" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L37" s="12"/>
       <c r="M37" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="2:14">
       <c r="B38" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J38" s="12"/>
       <c r="K38" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L38" s="12"/>
       <c r="M38" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N38" s="12"/>
     </row>
     <row r="39" spans="2:14">
       <c r="B39" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J39" s="12"/>
       <c r="K39" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N39" s="12"/>
     </row>
     <row r="40" spans="2:14">
       <c r="B40" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J40" s="12"/>
       <c r="K40" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L40" s="12"/>
       <c r="M40" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="2:14">
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J41" s="12"/>
       <c r="K41" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L41" s="12"/>
       <c r="M41" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N41" s="12"/>
     </row>
     <row r="42" spans="2:14">
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J42" s="12"/>
       <c r="K42" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L42" s="12"/>
       <c r="M42" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="2:14">
       <c r="B43" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J43" s="12"/>
       <c r="K43" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L43" s="12"/>
       <c r="M43" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N43" s="12"/>
     </row>
     <row r="44" spans="2:14">
       <c r="B44" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J44" s="12"/>
       <c r="K44" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L44" s="12"/>
       <c r="M44" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="2:14">
       <c r="B45" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J45" s="12"/>
       <c r="K45" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L45" s="12"/>
       <c r="M45" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="2:14">
       <c r="B46" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J46" s="12"/>
       <c r="K46" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L46" s="12"/>
       <c r="M46" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="2:14">
       <c r="B47" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J47" s="12"/>
       <c r="K47" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L47" s="12"/>
       <c r="M47" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="2:14">
       <c r="B48" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J48" s="12"/>
       <c r="K48" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12"/>
       <c r="M48" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="2:14">
       <c r="B49" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J49" s="12"/>
       <c r="K49" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L49" s="12"/>
       <c r="M49" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="2:14">
       <c r="B50" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J50" s="12"/>
       <c r="K50" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12"/>
       <c r="M50" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N50" s="12"/>
     </row>
     <row r="51" spans="2:14">
       <c r="B51" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J51" s="12"/>
       <c r="K51" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L51" s="12"/>
       <c r="M51" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N51" s="12"/>
     </row>
     <row r="52" spans="2:14">
       <c r="B52" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D52" s="12">
         <v>0</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="F52" s="12">
         <v>1</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="J52" s="12">
         <v>0</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="L52" s="12">
         <v>0</v>
       </c>
       <c r="M52" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="N52" s="12">
         <v>1</v>
@@ -2902,243 +2904,243 @@
     </row>
     <row r="53" spans="2:14">
       <c r="B53" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F53" s="12"/>
       <c r="G53" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J53" s="12"/>
       <c r="K53" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L53" s="12"/>
       <c r="M53" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N53" s="12"/>
     </row>
     <row r="54" spans="2:14">
       <c r="B54" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J54" s="12"/>
       <c r="K54" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L54" s="12"/>
       <c r="M54" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N54" s="12"/>
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J55" s="12"/>
       <c r="K55" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L55" s="12"/>
       <c r="M55" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N55" s="12"/>
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J56" s="12"/>
       <c r="K56" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L56" s="12"/>
       <c r="M56" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J57" s="12"/>
       <c r="K57" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N57" s="12"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J58" s="12"/>
       <c r="K58" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J59" s="12"/>
       <c r="K59" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L59" s="12"/>
       <c r="M59" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="2:14">
       <c r="B60" s="6" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D60" s="12">
         <v>1</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="F60" s="12">
         <v>1</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="H60" s="12">
         <v>1</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="J60" s="12">
         <v>1</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L60" s="12">
         <v>0</v>
       </c>
       <c r="M60" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="N60" s="12">
         <v>1</v>
@@ -3146,40 +3148,40 @@
     </row>
     <row r="61" spans="2:14">
       <c r="B61" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="F61" s="12">
         <v>1</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="H61" s="12">
         <v>1</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="J61" s="12">
         <v>1</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L61" s="12">
         <v>0</v>
       </c>
       <c r="M61" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="N61" s="12">
         <v>1</v>
@@ -3187,272 +3189,272 @@
     </row>
     <row r="62" spans="2:14">
       <c r="B62" s="2" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J62" s="12"/>
       <c r="K62" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="2:14">
       <c r="B63" s="4" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F63" s="12"/>
       <c r="G63" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H63" s="12"/>
       <c r="I63" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J63" s="12"/>
       <c r="K63" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L63" s="12"/>
       <c r="M63" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N63" s="12"/>
     </row>
     <row r="64" spans="2:14">
       <c r="B64" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F64" s="12"/>
       <c r="G64" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H64" s="12"/>
       <c r="I64" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J64" s="12"/>
       <c r="K64" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="2:14">
       <c r="B65" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H65" s="12"/>
       <c r="I65" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J65" s="12"/>
       <c r="K65" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L65" s="12"/>
       <c r="M65" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="2:14">
       <c r="B66" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H66" s="12"/>
       <c r="I66" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J66" s="12"/>
       <c r="K66" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N66" s="12"/>
     </row>
     <row r="67" spans="2:14">
       <c r="B67" s="7" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J67" s="12"/>
       <c r="K67" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N67" s="12"/>
     </row>
     <row r="68" spans="2:14">
       <c r="B68" s="7" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H68" s="12"/>
       <c r="I68" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J68" s="12"/>
       <c r="K68" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L68" s="12"/>
       <c r="M68" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N68" s="12"/>
     </row>
     <row r="69" spans="2:14">
       <c r="B69" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H69" s="12"/>
       <c r="I69" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J69" s="12"/>
       <c r="K69" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L69" s="12"/>
       <c r="M69" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N69" s="12"/>
     </row>
     <row r="70" spans="2:14">
       <c r="B70" s="4" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D70" s="12">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="F70" s="12">
         <v>1</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="H70" s="12">
         <v>1</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="J70" s="12">
         <v>1</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="L70" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="N70" s="12">
         <v>1</v>
@@ -3460,1489 +3462,1385 @@
     </row>
     <row r="71" spans="2:14">
       <c r="B71" s="2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F71" s="12"/>
       <c r="G71" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H71" s="12"/>
       <c r="I71" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J71" s="12"/>
       <c r="K71" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L71" s="12"/>
       <c r="M71" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="2:14">
       <c r="B72" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F72" s="12"/>
       <c r="G72" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H72" s="12"/>
       <c r="I72" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J72" s="12"/>
       <c r="K72" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L72" s="12"/>
       <c r="M72" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="2:14">
       <c r="B73" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="D73" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J73" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" s="12">
         <v>0</v>
       </c>
-      <c r="E73" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F73" s="12">
-        <v>0</v>
-      </c>
-      <c r="G73" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="H73" s="12">
-        <v>0</v>
-      </c>
-      <c r="I73" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="J73" s="12">
-        <v>0</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="L73" s="12"/>
       <c r="M73" s="14" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="N73" s="12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="2:14">
-      <c r="B74" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D74" s="12">
-        <v>0</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F74" s="12">
-        <v>0</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="H74" s="12">
-        <v>0</v>
-      </c>
-      <c r="I74" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="J74" s="12">
-        <v>0</v>
-      </c>
+      <c r="B74" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="12"/>
+      <c r="E74" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="12"/>
+      <c r="I74" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J74" s="12"/>
       <c r="K74" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L74" s="12"/>
-      <c r="M74" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="N74" s="12">
-        <v>0</v>
-      </c>
+      <c r="M74" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N74" s="12"/>
     </row>
     <row r="75" spans="2:14">
-      <c r="B75" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D75" s="12">
-        <v>1</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F75" s="12">
-        <v>1</v>
-      </c>
-      <c r="G75" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="H75" s="12">
-        <v>1</v>
-      </c>
-      <c r="I75" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="J75" s="12">
-        <v>0.9</v>
-      </c>
+      <c r="B75" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="12"/>
+      <c r="E75" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75" s="12"/>
+      <c r="I75" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" s="12"/>
       <c r="K75" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="L75" s="12">
-        <v>0</v>
-      </c>
-      <c r="M75" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="N75" s="12">
-        <v>1</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L75" s="12"/>
+      <c r="M75" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N75" s="12"/>
     </row>
     <row r="76" spans="2:14">
-      <c r="B76" s="4" t="s">
-        <v>73</v>
+      <c r="B76" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H76" s="12"/>
       <c r="I76" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J76" s="12"/>
       <c r="K76" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L76" s="12"/>
       <c r="M76" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="2:14">
-      <c r="B77" s="2" t="s">
-        <v>74</v>
+      <c r="B77" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D77" s="12"/>
       <c r="E77" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H77" s="12"/>
       <c r="I77" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J77" s="12"/>
       <c r="K77" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L77" s="12"/>
       <c r="M77" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="2:14">
       <c r="B78" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D78" s="12"/>
       <c r="E78" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H78" s="12"/>
       <c r="I78" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J78" s="12"/>
       <c r="K78" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L78" s="12"/>
       <c r="M78" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="2:14">
-      <c r="B79" s="2" t="s">
-        <v>76</v>
+      <c r="B79" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D79" s="12"/>
       <c r="E79" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F79" s="12"/>
       <c r="G79" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H79" s="12"/>
       <c r="I79" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J79" s="12"/>
       <c r="K79" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L79" s="12"/>
       <c r="M79" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="2:14">
-      <c r="B80" s="1" t="s">
-        <v>77</v>
+      <c r="B80" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F80" s="12"/>
       <c r="G80" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J80" s="12"/>
       <c r="K80" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L80" s="12"/>
       <c r="M80" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="2:14">
-      <c r="B81" s="2" t="s">
-        <v>78</v>
+      <c r="B81" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F81" s="12"/>
       <c r="G81" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H81" s="12"/>
       <c r="I81" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J81" s="12"/>
       <c r="K81" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L81" s="12"/>
       <c r="M81" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="2:14">
-      <c r="B82" s="1" t="s">
-        <v>79</v>
+      <c r="B82" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F82" s="12"/>
       <c r="G82" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H82" s="12"/>
       <c r="I82" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J82" s="12"/>
       <c r="K82" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L82" s="12"/>
       <c r="M82" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="2:14">
-      <c r="B83" s="2" t="s">
-        <v>80</v>
+      <c r="B83" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F83" s="12"/>
       <c r="G83" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H83" s="12"/>
       <c r="I83" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J83" s="12"/>
       <c r="K83" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L83" s="12"/>
       <c r="M83" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="2:14">
-      <c r="B84" s="1" t="s">
-        <v>81</v>
+      <c r="B84" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F84" s="12"/>
       <c r="G84" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H84" s="12"/>
       <c r="I84" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J84" s="12"/>
       <c r="K84" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L84" s="12"/>
       <c r="M84" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N84" s="12"/>
     </row>
     <row r="85" spans="2:14">
-      <c r="B85" s="4" t="s">
-        <v>82</v>
+      <c r="B85" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F85" s="12"/>
       <c r="G85" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H85" s="12"/>
       <c r="I85" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J85" s="12"/>
       <c r="K85" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L85" s="12"/>
       <c r="M85" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N85" s="12"/>
     </row>
     <row r="86" spans="2:14">
-      <c r="B86" s="1" t="s">
-        <v>83</v>
+      <c r="B86" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F86" s="12"/>
       <c r="G86" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H86" s="12"/>
       <c r="I86" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J86" s="12"/>
       <c r="K86" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L86" s="12"/>
       <c r="M86" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N86" s="12"/>
     </row>
     <row r="87" spans="2:14">
-      <c r="B87" s="2" t="s">
-        <v>84</v>
+      <c r="B87" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H87" s="12"/>
       <c r="I87" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J87" s="12"/>
       <c r="K87" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L87" s="12"/>
       <c r="M87" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N87" s="12"/>
     </row>
     <row r="88" spans="2:14">
-      <c r="B88" s="1" t="s">
-        <v>85</v>
+      <c r="B88" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F88" s="12"/>
       <c r="G88" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H88" s="12"/>
       <c r="I88" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J88" s="12"/>
       <c r="K88" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L88" s="12"/>
       <c r="M88" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N88" s="12"/>
     </row>
     <row r="89" spans="2:14">
-      <c r="B89" s="4" t="s">
-        <v>86</v>
+      <c r="B89" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F89" s="12"/>
       <c r="G89" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H89" s="12"/>
       <c r="I89" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J89" s="12"/>
       <c r="K89" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N89" s="12"/>
     </row>
     <row r="90" spans="2:14">
-      <c r="B90" s="4" t="s">
-        <v>87</v>
+      <c r="B90" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D90" s="12"/>
       <c r="E90" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F90" s="12"/>
       <c r="G90" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H90" s="12"/>
       <c r="I90" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J90" s="12"/>
       <c r="K90" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L90" s="12"/>
       <c r="M90" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N90" s="12"/>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="2" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F91" s="12"/>
       <c r="G91" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J91" s="12"/>
       <c r="K91" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L91" s="12"/>
       <c r="M91" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N91" s="12"/>
     </row>
     <row r="92" spans="2:14">
-      <c r="B92" s="1" t="s">
-        <v>89</v>
+      <c r="B92" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D92" s="12"/>
       <c r="E92" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F92" s="12"/>
       <c r="G92" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H92" s="12"/>
       <c r="I92" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J92" s="12"/>
       <c r="K92" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N92" s="12"/>
     </row>
     <row r="93" spans="2:14">
-      <c r="B93" s="2" t="s">
-        <v>90</v>
+      <c r="B93" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D93" s="12"/>
       <c r="E93" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F93" s="12"/>
       <c r="G93" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J93" s="12"/>
       <c r="K93" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L93" s="12"/>
       <c r="M93" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N93" s="12"/>
     </row>
     <row r="94" spans="2:14">
-      <c r="B94" s="2" t="s">
-        <v>91</v>
+      <c r="B94" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F94" s="12"/>
       <c r="G94" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J94" s="12"/>
       <c r="K94" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L94" s="12"/>
       <c r="M94" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N94" s="12"/>
     </row>
     <row r="95" spans="2:14">
-      <c r="B95" s="2" t="s">
-        <v>92</v>
+      <c r="B95" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F95" s="12"/>
       <c r="G95" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H95" s="12"/>
       <c r="I95" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J95" s="12"/>
       <c r="K95" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N95" s="12"/>
     </row>
     <row r="96" spans="2:14">
-      <c r="B96" s="4" t="s">
-        <v>93</v>
+      <c r="B96" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F96" s="12"/>
       <c r="G96" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H96" s="12"/>
       <c r="I96" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J96" s="12"/>
       <c r="K96" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L96" s="12"/>
       <c r="M96" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N96" s="12"/>
     </row>
     <row r="97" spans="2:14">
-      <c r="B97" s="5" t="s">
-        <v>94</v>
+      <c r="B97" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F97" s="12"/>
       <c r="G97" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H97" s="12"/>
       <c r="I97" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J97" s="12"/>
       <c r="K97" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L97" s="12"/>
       <c r="M97" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N97" s="12"/>
     </row>
     <row r="98" spans="2:14">
-      <c r="B98" s="1" t="s">
-        <v>95</v>
+      <c r="B98" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F98" s="12"/>
       <c r="G98" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H98" s="12"/>
       <c r="I98" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J98" s="12"/>
       <c r="K98" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L98" s="12"/>
       <c r="M98" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N98" s="12"/>
     </row>
     <row r="99" spans="2:14">
-      <c r="B99" s="2" t="s">
-        <v>96</v>
+      <c r="B99" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D99" s="12"/>
       <c r="E99" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F99" s="12"/>
       <c r="G99" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J99" s="12"/>
       <c r="K99" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L99" s="12"/>
       <c r="M99" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N99" s="12"/>
     </row>
     <row r="100" spans="2:14">
-      <c r="B100" s="1" t="s">
-        <v>97</v>
+      <c r="B100" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F100" s="12"/>
       <c r="G100" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H100" s="12"/>
       <c r="I100" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J100" s="12"/>
       <c r="K100" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L100" s="12"/>
       <c r="M100" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N100" s="12"/>
     </row>
     <row r="101" spans="2:14">
-      <c r="B101" s="2" t="s">
-        <v>98</v>
+      <c r="B101" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F101" s="12"/>
       <c r="G101" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H101" s="12"/>
       <c r="I101" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J101" s="12"/>
       <c r="K101" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L101" s="12"/>
       <c r="M101" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N101" s="12"/>
     </row>
     <row r="102" spans="2:14">
-      <c r="B102" s="1" t="s">
-        <v>99</v>
+      <c r="B102" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F102" s="12"/>
       <c r="G102" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H102" s="12"/>
       <c r="I102" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L102" s="12"/>
       <c r="M102" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N102" s="12"/>
     </row>
     <row r="103" spans="2:14">
-      <c r="B103" s="5" t="s">
-        <v>100</v>
+      <c r="B103" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D103" s="12"/>
       <c r="E103" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F103" s="12"/>
       <c r="G103" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J103" s="12"/>
       <c r="K103" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L103" s="12"/>
       <c r="M103" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N103" s="12"/>
     </row>
     <row r="104" spans="2:14">
-      <c r="B104" s="1" t="s">
-        <v>101</v>
+      <c r="B104" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D104" s="12"/>
       <c r="E104" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F104" s="12"/>
       <c r="G104" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J104" s="12"/>
       <c r="K104" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L104" s="12"/>
       <c r="M104" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N104" s="12"/>
     </row>
     <row r="105" spans="2:14">
-      <c r="B105" s="2" t="s">
-        <v>102</v>
+      <c r="B105" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D105" s="12"/>
       <c r="E105" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F105" s="12"/>
       <c r="G105" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J105" s="12"/>
       <c r="K105" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N105" s="12"/>
     </row>
     <row r="106" spans="2:14">
-      <c r="B106" s="1" t="s">
-        <v>103</v>
+      <c r="B106" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D106" s="12"/>
       <c r="E106" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F106" s="12"/>
       <c r="G106" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J106" s="12"/>
       <c r="K106" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L106" s="12"/>
       <c r="M106" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N106" s="12"/>
     </row>
     <row r="107" spans="2:14">
-      <c r="B107" s="2" t="s">
-        <v>104</v>
+      <c r="B107" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F107" s="12"/>
       <c r="G107" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J107" s="12"/>
       <c r="K107" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N107" s="12"/>
     </row>
     <row r="108" spans="2:14">
-      <c r="B108" s="1" t="s">
-        <v>105</v>
+      <c r="B108" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F108" s="12"/>
       <c r="G108" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J108" s="12"/>
       <c r="K108" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L108" s="12"/>
       <c r="M108" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N108" s="12"/>
     </row>
     <row r="109" spans="2:14">
       <c r="B109" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F109" s="12"/>
       <c r="G109" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J109" s="12"/>
       <c r="K109" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L109" s="12"/>
       <c r="M109" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N109" s="12"/>
     </row>
     <row r="110" spans="2:14">
-      <c r="B110" s="1" t="s">
-        <v>107</v>
+      <c r="B110" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D110" s="12"/>
       <c r="E110" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F110" s="12"/>
       <c r="G110" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J110" s="12"/>
       <c r="K110" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N110" s="12"/>
     </row>
     <row r="111" spans="2:14">
-      <c r="B111" s="2" t="s">
-        <v>108</v>
+      <c r="B111" s="9" t="s">
+        <v>123</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F111" s="12"/>
       <c r="G111" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J111" s="12"/>
       <c r="K111" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L111" s="12"/>
       <c r="M111" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N111" s="12"/>
     </row>
     <row r="112" spans="2:14">
-      <c r="B112" s="2" t="s">
-        <v>109</v>
+      <c r="B112" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J112" s="12"/>
       <c r="K112" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L112" s="12"/>
       <c r="M112" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N112" s="12"/>
     </row>
     <row r="113" spans="2:14">
-      <c r="B113" s="8" t="s">
-        <v>110</v>
+      <c r="B113" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F113" s="12"/>
       <c r="G113" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J113" s="12"/>
       <c r="K113" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N113" s="12"/>
     </row>
     <row r="114" spans="2:14">
-      <c r="B114" s="9" t="s">
-        <v>111</v>
+      <c r="B114" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D114" s="12"/>
       <c r="E114" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F114" s="12"/>
       <c r="G114" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J114" s="12"/>
       <c r="K114" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L114" s="12"/>
       <c r="M114" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N114" s="12"/>
     </row>
     <row r="115" spans="2:14">
       <c r="B115" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F115" s="12"/>
       <c r="G115" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J115" s="12"/>
       <c r="K115" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L115" s="12"/>
       <c r="M115" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N115" s="12"/>
     </row>
     <row r="116" spans="2:14">
       <c r="B116" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F116" s="12"/>
       <c r="G116" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="J116" s="12"/>
       <c r="K116" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="L116" s="12"/>
       <c r="M116" s="10" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="N116" s="12"/>
     </row>
     <row r="117" spans="2:14">
       <c r="B117" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D117" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="D117" s="13"/>
       <c r="E117" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F117" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F117" s="13"/>
       <c r="G117" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H117" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="H117" s="13"/>
       <c r="I117" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J117" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="J117" s="13"/>
       <c r="K117" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="L117" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="L117" s="13"/>
       <c r="M117" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="N117" s="12"/>
-    </row>
-    <row r="118" spans="2:14">
-      <c r="B118" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D118" s="12"/>
-      <c r="E118" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F118" s="12"/>
-      <c r="G118" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H118" s="12"/>
-      <c r="I118" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J118" s="12"/>
-      <c r="K118" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="L118" s="12"/>
-      <c r="M118" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="N118" s="12"/>
-    </row>
-    <row r="119" spans="2:14">
-      <c r="B119" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D119" s="12"/>
-      <c r="E119" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F119" s="12"/>
-      <c r="G119" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H119" s="12"/>
-      <c r="I119" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J119" s="12"/>
-      <c r="K119" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="L119" s="12"/>
-      <c r="M119" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="N119" s="12"/>
-    </row>
-    <row r="120" spans="2:14">
-      <c r="B120" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D120" s="13"/>
-      <c r="E120" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F120" s="13"/>
-      <c r="G120" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H120" s="13"/>
-      <c r="I120" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J120" s="13"/>
-      <c r="K120" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="L120" s="13"/>
-      <c r="M120" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="N120" s="13"/>
-    </row>
+        <v>14</v>
+      </c>
+      <c r="N117" s="13"/>
+    </row>
+    <row r="118" spans="2:14" ht="14.25"/>
+    <row r="119" spans="2:14" ht="14.25"/>
+    <row r="120" spans="2:14" ht="14.25"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G120 I3:I120 K3:K120 C3:C120 E3:E120 M3:M120" xr:uid="{EED3058D-8EE4-4C50-9B07-06B10E3DD8DB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G117 I3:I117 K3:K117 C3:C117 E3:E117 M3:M117" xr:uid="{EED3058D-8EE4-4C50-9B07-06B10E3DD8DB}">
       <formula1>$Q$3:$Q$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4952,4 +4850,338 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101007E6F4AFE9A8B4449B5095C950A419D4D" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="afa6857a8fdc9fcf49aef38709ae2c38">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="64a5dda8-8b4a-44a6-9503-2197c7d172f4" xmlns:ns3="e7c47c40-fd94-44e2-807b-aa57d1cb4f71" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2b715e5d13c8af849bd03d3024a4f124" ns2:_="" ns3:_="">
+    <xsd:import namespace="64a5dda8-8b4a-44a6-9503-2197c7d172f4"/>
+    <xsd:import namespace="e7c47c40-fd94-44e2-807b-aa57d1cb4f71"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:Fecha" minOccurs="0"/>
+                <xsd:element ref="ns2:Grupo" minOccurs="0"/>
+                <xsd:element ref="ns2:Fechamodificaci_x00f3_n" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="64a5dda8-8b4a-44a6-9503-2197c7d172f4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="19" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="20" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9edf088c-3f8a-459d-848d-4665e1a51e2e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Fecha" ma:index="27" nillable="true" ma:displayName="Fecha" ma:format="DateOnly" ma:internalName="Fecha">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Grupo" ma:index="28" nillable="true" ma:displayName="Grupo" ma:format="Dropdown" ma:list="UserInfo" ma:SharePointGroup="0" ma:internalName="Grupo">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:User">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="Fechamodificaci_x00f3_n" ma:index="29" nillable="true" ma:displayName="Fecha modificación" ma:format="DateOnly" ma:internalName="Fechamodificaci_x00f3_n">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e7c47c40-fd94-44e2-807b-aa57d1cb4f71" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a37b74d7-22fd-4a6c-96a7-4632356ed634}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e7c47c40-fd94-44e2-807b-aa57d1cb4f71">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Fechamodificaci_x00f3_n xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e7c47c40-fd94-44e2-807b-aa57d1cb4f71" xsi:nil="true"/>
+    <Fecha xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4" xsi:nil="true"/>
+    <Grupo xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Grupo>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8946A969-D939-4330-8A8E-554BA21E5624}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{187F26EF-178D-4B87-96D7-096ED7328CD1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{641C4330-7E61-4DB2-A773-8A186DF3964E}"/>
 </file>
--- a/data_src/Base_emprendimientos.xlsx
+++ b/data_src/Base_emprendimientos.xlsx
@@ -1,46 +1,383 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tzafon-my.sharepoint.com/personal/msagarraga_construirsa_com/Documents/Manuel Sagarraga/Planificación/Tableros/Loteos y edificios/Formato Nuevo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manuel Sagarraga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{6EF89FA6-8714-4E0D-BE98-228CB08B1897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF51B93-58BB-4FD8-A89A-CB4EAF68816F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1347DCAE-EC0F-4C2A-BEC9-AF374D732E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{186321B6-1986-4846-B637-EA981D8166FA}"/>
   </bookViews>
   <sheets>
     <sheet name="ID-Pipeline" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="133">
   <si>
     <t>Id Pipeline</t>
   </si>
   <si>
+    <t xml:space="preserve">VCC - Terreno 5Ha </t>
+  </si>
+  <si>
+    <t>VCC - Subdivisión Sur - Fortaleza &amp; Laurel - Sector Oeste</t>
+  </si>
+  <si>
+    <t>VCC - Subdivisión Sur - Aurora - Sector Macrolotes</t>
+  </si>
+  <si>
+    <t>VCC - Subdivisión Sur - Alegría &amp; Sendero - Sector Este</t>
+  </si>
+  <si>
+    <t>VCC - Town VI</t>
+  </si>
+  <si>
+    <t>VCC - Town V</t>
+  </si>
+  <si>
+    <t>VCC - Town IV</t>
+  </si>
+  <si>
+    <t>VCC - Town III</t>
+  </si>
+  <si>
+    <t>VCC - Town II</t>
+  </si>
+  <si>
+    <t>VCC - Town I</t>
+  </si>
+  <si>
+    <t>VCC - Los Juegos</t>
+  </si>
+  <si>
+    <t>Panamá - Marcos Tower</t>
+  </si>
+  <si>
+    <t>Py - Tierras de Luque</t>
+  </si>
+  <si>
+    <t>VCC - Los Arcos y Los Saltos</t>
+  </si>
+  <si>
+    <t>VCC - La Aventura</t>
+  </si>
+  <si>
+    <t>VCC - El Equipo</t>
+  </si>
+  <si>
+    <t>VCC - Aire Puro</t>
+  </si>
+  <si>
+    <t>Nxx - Tucumán Edificio 9</t>
+  </si>
+  <si>
+    <t>Nxx - Tucumán Edificio 8</t>
+  </si>
+  <si>
+    <t>Nxx - Torre Neuquén 6</t>
+  </si>
+  <si>
+    <t>Nxx - Torre Neuquén 5</t>
+  </si>
+  <si>
+    <t>Nxx - Torre Chubut III</t>
+  </si>
+  <si>
+    <t>Nxx - San Juan Edificio 4</t>
+  </si>
+  <si>
+    <t>Nxx - Salta Edificio 9</t>
+  </si>
+  <si>
+    <t>Nxx - Salta Edificio 10</t>
+  </si>
+  <si>
+    <t>Nxx - Loteo Tucuman</t>
+  </si>
+  <si>
+    <t>Nxx - Loteo Neuquén Norte</t>
+  </si>
+  <si>
+    <t>Nxx - Loteo Luján</t>
+  </si>
+  <si>
+    <t>Natania 52-Anzoategui 245</t>
+  </si>
+  <si>
+    <t>Natania 51-Los Alamos II</t>
+  </si>
+  <si>
+    <t>Natania 50-Beltran 411</t>
+  </si>
+  <si>
+    <t>Natania 49-Avellaneda 585</t>
+  </si>
+  <si>
+    <t>Natania 46-Aberastain Sur 414</t>
+  </si>
+  <si>
+    <t>Natania 45-Azcuénaga</t>
+  </si>
+  <si>
+    <t>Natania 29-Residencial II Sur</t>
+  </si>
+  <si>
+    <t>Natania 29-Residencial II</t>
+  </si>
+  <si>
+    <t>Natania 25 -Lujan</t>
+  </si>
+  <si>
+    <t>N92 - Nuevo Maipú II</t>
+  </si>
+  <si>
+    <t>N91 - Meglioli II</t>
+  </si>
+  <si>
+    <t>N90 - Py Tierras de Luque</t>
+  </si>
+  <si>
+    <t>N89 - Mate de Luna</t>
+  </si>
+  <si>
+    <t>N88 - Urquiza 265</t>
+  </si>
+  <si>
+    <t>N87 - España 1566</t>
+  </si>
+  <si>
+    <t>N86 - Santisima Trinidad</t>
+  </si>
+  <si>
+    <t>N85 - Molas López</t>
+  </si>
+  <si>
+    <t>N84 - Anzoategui III</t>
+  </si>
+  <si>
+    <t>N83 - Tomba 90</t>
+  </si>
+  <si>
+    <t>N82 - Alem 121 (II)</t>
+  </si>
+  <si>
+    <t>N81 - CH Rodríguez IV</t>
+  </si>
+  <si>
+    <t>N80 - Los Nogales II</t>
+  </si>
+  <si>
+    <t>N79 - Guemes</t>
+  </si>
+  <si>
+    <t>N78 - Dorrego</t>
+  </si>
+  <si>
+    <t>N77 - Ignacio de la Roza II (Sur)</t>
+  </si>
+  <si>
+    <t>N77 - Ignacio de la Roza II (Norte)</t>
+  </si>
+  <si>
+    <t>N77 - Ignacio de la Roza II (Mitre)</t>
+  </si>
+  <si>
+    <t>N76 - Celedonio Gutierrez</t>
+  </si>
+  <si>
+    <t>N75 - Arenales 155</t>
+  </si>
+  <si>
+    <t>N74 - Santa Lucía II</t>
+  </si>
+  <si>
+    <t>N73 - Nuevo Maipú</t>
+  </si>
+  <si>
+    <t>N72 - C. H. Rodríguez III</t>
+  </si>
+  <si>
+    <t>N71 - Camino a San Agustín</t>
+  </si>
+  <si>
+    <t>N70 - Anzoátegui II</t>
+  </si>
+  <si>
+    <t>N69 - Alem</t>
+  </si>
+  <si>
+    <t>N68 - Vicente López</t>
+  </si>
+  <si>
+    <t>N67 - Nuevo Guaymallen - B° La Aventura</t>
+  </si>
+  <si>
+    <t>N67 - Nuevo Guaymallen-B° Aire Puro</t>
+  </si>
+  <si>
+    <t>N67 - Nuevo Guaymallen - B° El Equipo</t>
+  </si>
+  <si>
+    <t>N64 - C. H. Rodríguez II</t>
+  </si>
+  <si>
+    <t>N63 - Crouzeilles</t>
+  </si>
+  <si>
+    <t>N62 - Carrodilla Sector Sur - Etapa II M</t>
+  </si>
+  <si>
+    <t>N62 - Carrodilla Sector Sur - Etapa II</t>
+  </si>
+  <si>
+    <t>N62 - Carrodilla Sector Norte</t>
+  </si>
+  <si>
+    <t>N61 - Leguizamón - III</t>
+  </si>
+  <si>
+    <t>N61 - Leguizamón - II</t>
+  </si>
+  <si>
+    <t>N61 - Leguizamón - I</t>
+  </si>
+  <si>
+    <t>N60 - Juramento</t>
+  </si>
+  <si>
+    <t>N59 - Avellaneda II</t>
+  </si>
+  <si>
+    <t>N58 - Dúplex Drummond - Etapa II</t>
+  </si>
+  <si>
+    <t>N58 - Dúplex Drummond</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - Viviendas - IV</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - Viviendas - III (Futura)</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - Viviendas - III</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - Viviendas - II</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - Viviendas - I</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - II</t>
+  </si>
+  <si>
+    <t>N58 - Drummond - I</t>
+  </si>
+  <si>
+    <t>N57 - Ignacio de la Roza</t>
+  </si>
+  <si>
+    <t>N56 - Francia</t>
+  </si>
+  <si>
+    <t>N55 - C. H. Rodríguez I</t>
+  </si>
+  <si>
+    <t>N54 - 9 de Julio</t>
+  </si>
+  <si>
+    <t>N53 - Prospero García</t>
+  </si>
+  <si>
+    <t>N48 - Los Nogales</t>
+  </si>
+  <si>
+    <t>N47 - Maipú</t>
+  </si>
+  <si>
+    <t>N44 - VCM-Viviendas-I (B° El Recreo)</t>
+  </si>
+  <si>
+    <t>N44 - VCM - Los Juegos</t>
+  </si>
+  <si>
+    <t>N44 - VCM - La Aventura</t>
+  </si>
+  <si>
+    <t>N44 - VCM - B° La Amistad</t>
+  </si>
+  <si>
+    <t>N44 - VCM - El Recreo</t>
+  </si>
+  <si>
+    <t>N24 - Santa Lucia</t>
+  </si>
+  <si>
+    <t>N23 - Guaymallén - IV</t>
+  </si>
+  <si>
+    <t>N21 - Matienzo</t>
+  </si>
+  <si>
+    <t>N19 - Valle Escondido</t>
+  </si>
+  <si>
+    <t>Mil Aires - Edificio V</t>
+  </si>
+  <si>
+    <t>Mil Aires - Edificio IV</t>
+  </si>
+  <si>
+    <t>Mil Aires - Edificio III</t>
+  </si>
+  <si>
+    <t>Mil Aires - Edificio II</t>
+  </si>
+  <si>
+    <t>Mil Aires - Edificio I</t>
+  </si>
+  <si>
+    <t>Nobleza</t>
+  </si>
+  <si>
+    <t>7-Entregado</t>
+  </si>
+  <si>
+    <t>1-A la espera de Minuta-Terreno-Definicion Comercial</t>
+  </si>
+  <si>
+    <t>N44 - VCM - La Victoria</t>
+  </si>
+  <si>
+    <t>N44 - VCM - El Triunfo</t>
+  </si>
+  <si>
+    <t>VCC - La Victoria</t>
+  </si>
+  <si>
+    <t>VCC - El Triunfo</t>
+  </si>
+  <si>
+    <t>VCC - El Recreo</t>
+  </si>
+  <si>
+    <t>VCC - La Amistad</t>
+  </si>
+  <si>
     <t>Tiene Gas</t>
   </si>
   <si>
@@ -71,361 +408,22 @@
     <t>Porcentaje avance obra Espacios Verdes</t>
   </si>
   <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Tiene red vial</t>
   </si>
   <si>
     <t>Porcentaje avance obra Red Vial</t>
   </si>
   <si>
-    <t xml:space="preserve">VCC - Terreno 5Ha </t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>VCC - Subdivisión Sur - Fortaleza &amp; Laurel - Sector Oeste</t>
-  </si>
-  <si>
-    <t>VCC - Subdivisión Sur - Aurora - Sector Macrolotes</t>
-  </si>
-  <si>
-    <t>VCC - Subdivisión Sur - Alegría &amp; Sendero - Sector Este</t>
-  </si>
-  <si>
-    <t>VCC - Town VI</t>
-  </si>
-  <si>
-    <t>VCC - Town V</t>
-  </si>
-  <si>
-    <t>VCC - Town IV</t>
-  </si>
-  <si>
-    <t>VCC - Town III</t>
-  </si>
-  <si>
-    <t>VCC - Town II</t>
-  </si>
-  <si>
-    <t>VCC - Town I</t>
-  </si>
-  <si>
-    <t>VCC - Los Juegos</t>
-  </si>
-  <si>
-    <t>Panamá - Marcos Tower</t>
-  </si>
-  <si>
-    <t>Py - Tierras de Luque</t>
-  </si>
-  <si>
-    <t>VCC - Los Arcos y Los Saltos</t>
-  </si>
-  <si>
-    <t>VCC - La Aventura</t>
-  </si>
-  <si>
-    <t>VCC - El Equipo</t>
-  </si>
-  <si>
-    <t>VCC - Aire Puro</t>
-  </si>
-  <si>
-    <t>Nxx - Tucumán Edificio 9</t>
-  </si>
-  <si>
-    <t>Nxx - Tucumán Edificio 8</t>
-  </si>
-  <si>
-    <t>Nxx - Torre Neuquén 6</t>
-  </si>
-  <si>
-    <t>Nxx - Torre Neuquén 5</t>
-  </si>
-  <si>
-    <t>Nxx - Torre Chubut III</t>
-  </si>
-  <si>
-    <t>Nxx - San Juan Edificio 4</t>
-  </si>
-  <si>
-    <t>Nxx - Salta Edificio 9</t>
-  </si>
-  <si>
-    <t>Nxx - Salta Edificio 10</t>
-  </si>
-  <si>
-    <t>Nxx - Loteo Tucuman</t>
-  </si>
-  <si>
-    <t>Nxx - Loteo Neuquén Norte</t>
-  </si>
-  <si>
-    <t>Nxx - Loteo Luján</t>
-  </si>
-  <si>
-    <t>Natania 52-Anzoategui 245</t>
-  </si>
-  <si>
-    <t>Natania 51-Los Alamos II</t>
-  </si>
-  <si>
-    <t>Natania 50-Beltran 411</t>
-  </si>
-  <si>
-    <t>Natania 49-Avellaneda 585</t>
-  </si>
-  <si>
-    <t>Natania 46-Aberastain Sur 414</t>
-  </si>
-  <si>
-    <t>Natania 45-Azcuénaga</t>
-  </si>
-  <si>
-    <t>Natania 29-Residencial II Sur</t>
-  </si>
-  <si>
-    <t>Natania 29-Residencial II</t>
-  </si>
-  <si>
-    <t>Natania 25 -Lujan</t>
-  </si>
-  <si>
-    <t>N92 - Nuevo Maipú II</t>
-  </si>
-  <si>
-    <t>N91 - Meglioli II</t>
-  </si>
-  <si>
-    <t>N90 - Py Tierras de Luque</t>
-  </si>
-  <si>
-    <t>N89 - Mate de Luna</t>
-  </si>
-  <si>
-    <t>N88 - Urquiza 265</t>
-  </si>
-  <si>
-    <t>N87 - España 1566</t>
-  </si>
-  <si>
-    <t>N86 - Santisima Trinidad</t>
-  </si>
-  <si>
-    <t>N85 - Molas López</t>
-  </si>
-  <si>
-    <t>N84 - Anzoategui III</t>
-  </si>
-  <si>
-    <t>N83 - Tomba 90</t>
-  </si>
-  <si>
-    <t>N82 - Alem 121 (II)</t>
-  </si>
-  <si>
-    <t>N81 - CH Rodríguez IV</t>
-  </si>
-  <si>
-    <t>N80 - Los Nogales II</t>
-  </si>
-  <si>
-    <t>N79 - Guemes</t>
-  </si>
-  <si>
-    <t>N78 - Dorrego</t>
-  </si>
-  <si>
-    <t>N77 - Ignacio de la Roza II (Sur)</t>
-  </si>
-  <si>
-    <t>N77 - Ignacio de la Roza II (Norte)</t>
-  </si>
-  <si>
-    <t>N77 - Ignacio de la Roza II (Mitre)</t>
-  </si>
-  <si>
-    <t>N76 - Celedonio Gutierrez</t>
-  </si>
-  <si>
-    <t>N75 - Arenales 155</t>
-  </si>
-  <si>
-    <t>N74 - Santa Lucía II</t>
-  </si>
-  <si>
-    <t>N73 - Nuevo Maipú</t>
-  </si>
-  <si>
-    <t>N72 - C. H. Rodríguez III</t>
-  </si>
-  <si>
-    <t>N71 - Camino a San Agustín</t>
-  </si>
-  <si>
-    <t>N70 - Anzoátegui II</t>
-  </si>
-  <si>
-    <t>N69 - Alem</t>
-  </si>
-  <si>
-    <t>N68 - Vicente López</t>
-  </si>
-  <si>
-    <t>N67 - Nuevo Guaymallen - B° La Aventura</t>
-  </si>
-  <si>
-    <t>N67 - Nuevo Guaymallen-B° Aire Puro</t>
-  </si>
-  <si>
-    <t>N67 - Nuevo Guaymallen - B° El Equipo</t>
-  </si>
-  <si>
     <t>N65 - Meglioli</t>
   </si>
   <si>
-    <t>N64 - C. H. Rodríguez II</t>
-  </si>
-  <si>
-    <t>N63 - Crouzeilles</t>
-  </si>
-  <si>
     <t>N62 - Carrodilla Sector Sur</t>
-  </si>
-  <si>
-    <t>N61 - Leguizamón - III</t>
-  </si>
-  <si>
-    <t>N61 - Leguizamón - II</t>
-  </si>
-  <si>
-    <t>N61 - Leguizamón - I</t>
-  </si>
-  <si>
-    <t>N60 - Juramento</t>
-  </si>
-  <si>
-    <t>N59 - Avellaneda II</t>
-  </si>
-  <si>
-    <t>N58 - Dúplex Drummond - Etapa II</t>
-  </si>
-  <si>
-    <t>N58 - Dúplex Drummond</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - Viviendas - IV</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - Viviendas - III (Futura)</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - Viviendas - III</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - Viviendas - II</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - Viviendas - I</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - II</t>
-  </si>
-  <si>
-    <t>N58 - Drummond - I</t>
-  </si>
-  <si>
-    <t>N57 - Ignacio de la Roza</t>
-  </si>
-  <si>
-    <t>N56 - Francia</t>
-  </si>
-  <si>
-    <t>N55 - C. H. Rodríguez I</t>
-  </si>
-  <si>
-    <t>N54 - 9 de Julio</t>
-  </si>
-  <si>
-    <t>N53 - Prospero García</t>
-  </si>
-  <si>
-    <t>N48 - Los Nogales</t>
-  </si>
-  <si>
-    <t>N47 - Maipú</t>
-  </si>
-  <si>
-    <t>N44 - VCM-Viviendas-I (B° El Recreo)</t>
-  </si>
-  <si>
-    <t>N44 - VCM - Los Juegos</t>
-  </si>
-  <si>
-    <t>N44 - VCM - La Aventura</t>
-  </si>
-  <si>
-    <t>N44 - VCM - B° La Amistad</t>
-  </si>
-  <si>
-    <t>N44 - VCM - El Recreo</t>
-  </si>
-  <si>
-    <t>N24 - Santa Lucia</t>
-  </si>
-  <si>
-    <t>N23 - Guaymallén - IV</t>
-  </si>
-  <si>
-    <t>N21 - Matienzo</t>
-  </si>
-  <si>
-    <t>N19 - Valle Escondido</t>
-  </si>
-  <si>
-    <t>Mil Aires - Edificio V</t>
-  </si>
-  <si>
-    <t>Mil Aires - Edificio IV</t>
-  </si>
-  <si>
-    <t>Mil Aires - Edificio III</t>
-  </si>
-  <si>
-    <t>Mil Aires - Edificio II</t>
-  </si>
-  <si>
-    <t>Mil Aires - Edificio I</t>
-  </si>
-  <si>
-    <t>Nobleza</t>
-  </si>
-  <si>
-    <t>7-Entregado</t>
-  </si>
-  <si>
-    <t>1-A la espera de Minuta-Terreno-Definicion Comercial</t>
-  </si>
-  <si>
-    <t>N44 - VCM - La Victoria</t>
-  </si>
-  <si>
-    <t>N44 - VCM - El Triunfo</t>
-  </si>
-  <si>
-    <t>VCC - La Victoria</t>
-  </si>
-  <si>
-    <t>VCC - El Triunfo</t>
-  </si>
-  <si>
-    <t>VCC - El Recreo</t>
-  </si>
-  <si>
-    <t>VCC - La Amistad</t>
   </si>
 </sst>
 </file>
@@ -569,7 +567,317 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -601,42 +909,6 @@
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top/>
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
@@ -700,9 +972,9 @@
         <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -710,7 +982,9 @@
           <color theme="4" tint="0.39997558519241921"/>
         </left>
         <right/>
-        <top/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
@@ -774,42 +1048,6 @@
         <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
@@ -823,116 +1061,6 @@
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top/>
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
@@ -1062,29 +1190,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C11D5BB-6E7F-495A-8630-57EEE9ED707D}" name="Tabla33" displayName="Tabla33" ref="B2:N117" totalsRowShown="0">
-  <autoFilter ref="B2:N117" xr:uid="{5EF82ADA-92C0-4046-9873-D007DF2DF3F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3C11D5BB-6E7F-495A-8630-57EEE9ED707D}" name="Tabla33" displayName="Tabla33" ref="B2:N120" totalsRowShown="0">
+  <autoFilter ref="B2:N120" xr:uid="{5EF82ADA-92C0-4046-9873-D007DF2DF3F2}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{CAFB1AD4-2693-485F-BE91-7365DB5C2907}" name="Id Pipeline" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{F9E3AE6C-CEBB-450A-8EC4-D886522B623F}" name="Tiene Gas" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{F3023337-9488-491B-A575-E3E9FAFAC300}" name="Porcentaje avance obra Gas" dataDxfId="10" dataCellStyle="Porcentaje"/>
-    <tableColumn id="4" xr3:uid="{06B5BC5C-D27E-4E38-9926-D51AE4FBFACD}" name="Tiene Agua" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{F6843E71-451C-43F2-B639-FC2FE7F1B471}" name="Porcentaje avance obra Agua" dataDxfId="8" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{C20CC36D-7740-4D2B-801F-82B19001E86D}" name="Tiene Cloacas" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{9A0144E1-04FE-41DD-9BEA-F333F71FF108}" name="Porcentaje avance obra Cloacas" dataDxfId="6" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{89F15495-2941-471D-94B2-3815C9CD9F01}" name="Tiene Electricidad e Iluminación" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{FE0B7B56-00A7-4471-94BE-A8EDE2A40208}" name="Porcentaje avance obra Electricidad e Iluminación" dataDxfId="4" dataCellStyle="Porcentaje"/>
+    <tableColumn id="1" xr3:uid="{CAFB1AD4-2693-485F-BE91-7365DB5C2907}" name="Id Pipeline" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{F9E3AE6C-CEBB-450A-8EC4-D886522B623F}" name="Tiene Gas" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{F3023337-9488-491B-A575-E3E9FAFAC300}" name="Porcentaje avance obra Gas" dataDxfId="23" dataCellStyle="Porcentaje"/>
+    <tableColumn id="4" xr3:uid="{06B5BC5C-D27E-4E38-9926-D51AE4FBFACD}" name="Tiene Agua" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{F6843E71-451C-43F2-B639-FC2FE7F1B471}" name="Porcentaje avance obra Agua" dataDxfId="22" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{C20CC36D-7740-4D2B-801F-82B19001E86D}" name="Tiene Cloacas" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{9A0144E1-04FE-41DD-9BEA-F333F71FF108}" name="Porcentaje avance obra Cloacas" dataDxfId="21" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{89F15495-2941-471D-94B2-3815C9CD9F01}" name="Tiene Electricidad e Iluminación" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{FE0B7B56-00A7-4471-94BE-A8EDE2A40208}" name="Porcentaje avance obra Electricidad e Iluminación" dataDxfId="20" dataCellStyle="Porcentaje"/>
     <tableColumn id="10" xr3:uid="{8D46E135-17D8-4BE0-889B-794186167EA6}" name="Tiene Espacios Verdes" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{F6CC6466-FF10-4CED-B787-08AAD4ABEFE0}" name="Porcentaje avance obra Espacios Verdes" dataDxfId="2" dataCellStyle="Porcentaje"/>
-    <tableColumn id="13" xr3:uid="{22A542C0-82D6-4920-926D-3ED6361E41CD}" name="Tiene red vial" dataDxfId="1" dataCellStyle="Porcentaje"/>
-    <tableColumn id="12" xr3:uid="{9CB86939-5531-4A47-93E4-76F29ED0C9A8}" name="Porcentaje avance obra Red Vial" dataDxfId="0" dataCellStyle="Porcentaje"/>
+    <tableColumn id="11" xr3:uid="{F6CC6466-FF10-4CED-B787-08AAD4ABEFE0}" name="Porcentaje avance obra Espacios Verdes" dataDxfId="19" dataCellStyle="Porcentaje"/>
+    <tableColumn id="13" xr3:uid="{22A542C0-82D6-4920-926D-3ED6361E41CD}" name="Tiene red vial" dataDxfId="0" dataCellStyle="Porcentaje"/>
+    <tableColumn id="12" xr3:uid="{9CB86939-5531-4A47-93E4-76F29ED0C9A8}" name="Porcentaje avance obra Red Vial" dataDxfId="18" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1381,18 +1509,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9896A896-5C32-4D49-B765-A86BFC70A98B}">
   <dimension ref="B2:Q120"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="64.5" customWidth="1"/>
-    <col min="4" max="4" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="28.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.69921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -1400,1503 +1529,1503 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="I2" t="s">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="J2" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="L2" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="M2" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="N2" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="2:17">
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L3" s="11"/>
       <c r="M3" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N3" s="11"/>
       <c r="Q3" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N4" s="12"/>
       <c r="Q4" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="2:17">
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="2:17">
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="2:17">
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="2:14">
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="2:14">
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="2:14" ht="15" customHeight="1">
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J20" s="12"/>
       <c r="K20" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="2:14">
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="2:14">
       <c r="B22" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="2:14">
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J25" s="12"/>
       <c r="K25" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="2:14">
       <c r="B26" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J26" s="12"/>
       <c r="K26" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="2:14">
       <c r="B27" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J27" s="12"/>
       <c r="K27" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="2:14">
       <c r="B28" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="2:14">
       <c r="B29" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="2:14">
       <c r="B30" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="2:14">
       <c r="B31" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="2:14">
       <c r="B32" s="4" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J32" s="12"/>
       <c r="K32" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L32" s="12"/>
       <c r="M32" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J33" s="12"/>
       <c r="K33" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L33" s="12"/>
       <c r="M33" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J34" s="12"/>
       <c r="K34" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L34" s="12"/>
       <c r="M34" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="2:14">
       <c r="B35" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J35" s="12"/>
       <c r="K35" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L35" s="12"/>
       <c r="M35" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="2:14">
       <c r="B36" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J36" s="12"/>
       <c r="K36" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L36" s="12"/>
       <c r="M36" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="2:14">
       <c r="B37" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J37" s="12"/>
       <c r="K37" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L37" s="12"/>
       <c r="M37" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="2:14">
       <c r="B38" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J38" s="12"/>
       <c r="K38" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L38" s="12"/>
       <c r="M38" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N38" s="12"/>
     </row>
     <row r="39" spans="2:14">
       <c r="B39" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J39" s="12"/>
       <c r="K39" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N39" s="12"/>
     </row>
     <row r="40" spans="2:14">
       <c r="B40" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J40" s="12"/>
       <c r="K40" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L40" s="12"/>
       <c r="M40" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="2:14">
       <c r="B41" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J41" s="12"/>
       <c r="K41" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L41" s="12"/>
       <c r="M41" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N41" s="12"/>
     </row>
     <row r="42" spans="2:14">
       <c r="B42" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J42" s="12"/>
       <c r="K42" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L42" s="12"/>
       <c r="M42" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="2:14">
       <c r="B43" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J43" s="12"/>
       <c r="K43" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L43" s="12"/>
       <c r="M43" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N43" s="12"/>
     </row>
     <row r="44" spans="2:14">
       <c r="B44" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J44" s="12"/>
       <c r="K44" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L44" s="12"/>
       <c r="M44" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="2:14">
       <c r="B45" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J45" s="12"/>
       <c r="K45" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L45" s="12"/>
       <c r="M45" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="2:14">
       <c r="B46" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J46" s="12"/>
       <c r="K46" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L46" s="12"/>
       <c r="M46" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="2:14">
       <c r="B47" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J47" s="12"/>
       <c r="K47" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L47" s="12"/>
       <c r="M47" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="2:14">
       <c r="B48" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J48" s="12"/>
       <c r="K48" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L48" s="12"/>
       <c r="M48" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="2:14">
       <c r="B49" s="2" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J49" s="12"/>
       <c r="K49" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L49" s="12"/>
       <c r="M49" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="2:14">
       <c r="B50" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J50" s="12"/>
       <c r="K50" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L50" s="12"/>
       <c r="M50" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N50" s="12"/>
     </row>
     <row r="51" spans="2:14">
       <c r="B51" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J51" s="12"/>
       <c r="K51" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L51" s="12"/>
       <c r="M51" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N51" s="12"/>
     </row>
     <row r="52" spans="2:14">
       <c r="B52" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D52" s="12">
         <v>0</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F52" s="12">
         <v>1</v>
       </c>
-      <c r="G52" s="10" t="s">
-        <v>14</v>
+      <c r="G52" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="J52" s="12">
         <v>0</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="L52" s="12">
         <v>0</v>
       </c>
       <c r="M52" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="N52" s="12">
         <v>1</v>
@@ -2904,243 +3033,243 @@
     </row>
     <row r="53" spans="2:14">
       <c r="B53" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F53" s="12"/>
       <c r="G53" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J53" s="12"/>
       <c r="K53" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L53" s="12"/>
       <c r="M53" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N53" s="12"/>
     </row>
     <row r="54" spans="2:14">
       <c r="B54" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J54" s="12"/>
       <c r="K54" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L54" s="12"/>
       <c r="M54" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N54" s="12"/>
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J55" s="12"/>
       <c r="K55" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L55" s="12"/>
       <c r="M55" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N55" s="12"/>
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J56" s="12"/>
       <c r="K56" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L56" s="12"/>
       <c r="M56" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J57" s="12"/>
       <c r="K57" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N57" s="12"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J58" s="12"/>
       <c r="K58" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N58" s="12"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J59" s="12"/>
       <c r="K59" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L59" s="12"/>
       <c r="M59" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N59" s="12"/>
     </row>
     <row r="60" spans="2:14">
       <c r="B60" s="6" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D60" s="12">
         <v>1</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F60" s="12">
         <v>1</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H60" s="12">
         <v>1</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="J60" s="12">
         <v>1</v>
       </c>
-      <c r="K60" s="10" t="s">
-        <v>14</v>
+      <c r="K60" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="L60" s="12">
         <v>0</v>
       </c>
       <c r="M60" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="N60" s="12">
         <v>1</v>
@@ -3148,40 +3277,40 @@
     </row>
     <row r="61" spans="2:14">
       <c r="B61" s="4" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F61" s="12">
         <v>1</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H61" s="12">
         <v>1</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="J61" s="12">
         <v>1</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L61" s="12">
         <v>0</v>
       </c>
       <c r="M61" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="N61" s="12">
         <v>1</v>
@@ -3189,272 +3318,284 @@
     </row>
     <row r="62" spans="2:14">
       <c r="B62" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J62" s="12"/>
       <c r="K62" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N62" s="12"/>
     </row>
     <row r="63" spans="2:14">
       <c r="B63" s="4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" s="12"/>
+        <v>128</v>
+      </c>
+      <c r="D63" s="12">
+        <v>0</v>
+      </c>
       <c r="E63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="12"/>
+        <v>127</v>
+      </c>
+      <c r="F63" s="12">
+        <v>1</v>
+      </c>
       <c r="G63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="12"/>
+        <v>127</v>
+      </c>
+      <c r="H63" s="12">
+        <v>1</v>
+      </c>
       <c r="I63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J63" s="12"/>
+        <v>127</v>
+      </c>
+      <c r="J63" s="12">
+        <v>0.9</v>
+      </c>
       <c r="K63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L63" s="12"/>
+        <v>127</v>
+      </c>
+      <c r="L63" s="12">
+        <v>0.1</v>
+      </c>
       <c r="M63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N63" s="12"/>
+        <v>127</v>
+      </c>
+      <c r="N63" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="2:14">
       <c r="B64" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F64" s="12"/>
       <c r="G64" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H64" s="12"/>
       <c r="I64" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J64" s="12"/>
       <c r="K64" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N64" s="12"/>
     </row>
     <row r="65" spans="2:14">
       <c r="B65" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H65" s="12"/>
       <c r="I65" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J65" s="12"/>
       <c r="K65" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L65" s="12"/>
       <c r="M65" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="2:14">
       <c r="B66" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H66" s="12"/>
       <c r="I66" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J66" s="12"/>
       <c r="K66" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N66" s="12"/>
     </row>
     <row r="67" spans="2:14">
       <c r="B67" s="7" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J67" s="12"/>
       <c r="K67" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N67" s="12"/>
     </row>
     <row r="68" spans="2:14">
       <c r="B68" s="7" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H68" s="12"/>
       <c r="I68" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J68" s="12"/>
       <c r="K68" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L68" s="12"/>
       <c r="M68" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N68" s="12"/>
     </row>
     <row r="69" spans="2:14">
       <c r="B69" s="4" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H69" s="12"/>
       <c r="I69" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J69" s="12"/>
       <c r="K69" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L69" s="12"/>
       <c r="M69" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N69" s="12"/>
     </row>
     <row r="70" spans="2:14">
       <c r="B70" s="4" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D70" s="12">
         <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F70" s="12">
         <v>1</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H70" s="12">
         <v>1</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="J70" s="12">
         <v>1</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="L70" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="N70" s="12">
         <v>1</v>
@@ -3462,1385 +3603,1537 @@
     </row>
     <row r="71" spans="2:14">
       <c r="B71" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F71" s="12"/>
       <c r="G71" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H71" s="12"/>
       <c r="I71" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J71" s="12"/>
       <c r="K71" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L71" s="12"/>
       <c r="M71" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N71" s="12"/>
     </row>
     <row r="72" spans="2:14">
       <c r="B72" s="4" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F72" s="12"/>
       <c r="G72" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H72" s="12"/>
       <c r="I72" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J72" s="12"/>
       <c r="K72" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L72" s="12"/>
       <c r="M72" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N72" s="12"/>
     </row>
     <row r="73" spans="2:14">
       <c r="B73" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D73" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F73" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H73" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="J73" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L73" s="12">
         <v>0</v>
       </c>
+      <c r="K73" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="L73" s="12"/>
       <c r="M73" s="14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="N73" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="2:14">
-      <c r="B74" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" s="12"/>
-      <c r="E74" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="12"/>
-      <c r="G74" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="12"/>
-      <c r="I74" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J74" s="12"/>
-      <c r="K74" s="10" t="s">
-        <v>14</v>
+      <c r="B74" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D74" s="12">
+        <v>0</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F74" s="12">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H74" s="12">
+        <v>0</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J74" s="12">
+        <v>0</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="L74" s="12"/>
-      <c r="M74" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N74" s="12"/>
+      <c r="M74" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="N74" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="2:14">
-      <c r="B75" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" s="12"/>
-      <c r="E75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="12"/>
-      <c r="I75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J75" s="12"/>
-      <c r="K75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L75" s="12"/>
-      <c r="M75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N75" s="12"/>
+      <c r="B75" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D75" s="12">
+        <v>1</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F75" s="12">
+        <v>1</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H75" s="12">
+        <v>1</v>
+      </c>
+      <c r="I75" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J75" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="L75" s="12">
+        <v>0</v>
+      </c>
+      <c r="M75" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="N75" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="2:14">
-      <c r="B76" s="2" t="s">
-        <v>88</v>
+      <c r="B76" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H76" s="12"/>
       <c r="I76" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J76" s="12"/>
       <c r="K76" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L76" s="12"/>
       <c r="M76" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N76" s="12"/>
     </row>
     <row r="77" spans="2:14">
-      <c r="B77" s="1" t="s">
-        <v>89</v>
+      <c r="B77" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D77" s="12"/>
       <c r="E77" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H77" s="12"/>
       <c r="I77" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J77" s="12"/>
       <c r="K77" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L77" s="12"/>
       <c r="M77" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N77" s="12"/>
     </row>
     <row r="78" spans="2:14">
       <c r="B78" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D78" s="12"/>
       <c r="E78" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H78" s="12"/>
       <c r="I78" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J78" s="12"/>
       <c r="K78" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L78" s="12"/>
       <c r="M78" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="2:14">
-      <c r="B79" s="1" t="s">
-        <v>91</v>
+      <c r="B79" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D79" s="12"/>
       <c r="E79" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F79" s="12"/>
       <c r="G79" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H79" s="12"/>
       <c r="I79" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J79" s="12"/>
       <c r="K79" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L79" s="12"/>
       <c r="M79" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="2:14">
-      <c r="B80" s="2" t="s">
-        <v>92</v>
+      <c r="B80" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F80" s="12"/>
       <c r="G80" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J80" s="12"/>
       <c r="K80" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L80" s="12"/>
       <c r="M80" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N80" s="12"/>
     </row>
     <row r="81" spans="2:14">
-      <c r="B81" s="1" t="s">
-        <v>93</v>
+      <c r="B81" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F81" s="12"/>
       <c r="G81" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H81" s="12"/>
       <c r="I81" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J81" s="12"/>
       <c r="K81" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L81" s="12"/>
       <c r="M81" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N81" s="12"/>
     </row>
     <row r="82" spans="2:14">
-      <c r="B82" s="4" t="s">
-        <v>94</v>
+      <c r="B82" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F82" s="12"/>
       <c r="G82" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H82" s="12"/>
       <c r="I82" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J82" s="12"/>
       <c r="K82" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L82" s="12"/>
       <c r="M82" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N82" s="12"/>
     </row>
     <row r="83" spans="2:14">
-      <c r="B83" s="1" t="s">
-        <v>95</v>
+      <c r="B83" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F83" s="12"/>
       <c r="G83" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H83" s="12"/>
       <c r="I83" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J83" s="12"/>
       <c r="K83" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L83" s="12"/>
       <c r="M83" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N83" s="12"/>
     </row>
     <row r="84" spans="2:14">
-      <c r="B84" s="2" t="s">
-        <v>96</v>
+      <c r="B84" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F84" s="12"/>
       <c r="G84" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H84" s="12"/>
       <c r="I84" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J84" s="12"/>
       <c r="K84" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L84" s="12"/>
       <c r="M84" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N84" s="12"/>
     </row>
     <row r="85" spans="2:14">
-      <c r="B85" s="1" t="s">
-        <v>97</v>
+      <c r="B85" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F85" s="12"/>
       <c r="G85" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H85" s="12"/>
       <c r="I85" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J85" s="12"/>
       <c r="K85" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L85" s="12"/>
       <c r="M85" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N85" s="12"/>
     </row>
     <row r="86" spans="2:14">
-      <c r="B86" s="4" t="s">
-        <v>98</v>
+      <c r="B86" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F86" s="12"/>
       <c r="G86" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H86" s="12"/>
       <c r="I86" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J86" s="12"/>
       <c r="K86" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L86" s="12"/>
       <c r="M86" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N86" s="12"/>
     </row>
     <row r="87" spans="2:14">
-      <c r="B87" s="4" t="s">
-        <v>99</v>
+      <c r="B87" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H87" s="12"/>
       <c r="I87" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J87" s="12"/>
       <c r="K87" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L87" s="12"/>
       <c r="M87" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N87" s="12"/>
     </row>
     <row r="88" spans="2:14">
-      <c r="B88" s="2" t="s">
-        <v>100</v>
+      <c r="B88" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F88" s="12"/>
       <c r="G88" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H88" s="12"/>
       <c r="I88" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J88" s="12"/>
       <c r="K88" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L88" s="12"/>
       <c r="M88" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N88" s="12"/>
     </row>
     <row r="89" spans="2:14">
-      <c r="B89" s="1" t="s">
-        <v>101</v>
+      <c r="B89" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F89" s="12"/>
       <c r="G89" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H89" s="12"/>
       <c r="I89" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J89" s="12"/>
       <c r="K89" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N89" s="12"/>
     </row>
     <row r="90" spans="2:14">
-      <c r="B90" s="2" t="s">
-        <v>102</v>
+      <c r="B90" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D90" s="12"/>
       <c r="E90" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F90" s="12"/>
       <c r="G90" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H90" s="12"/>
       <c r="I90" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J90" s="12"/>
       <c r="K90" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L90" s="12"/>
       <c r="M90" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N90" s="12"/>
     </row>
     <row r="91" spans="2:14">
       <c r="B91" s="2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F91" s="12"/>
       <c r="G91" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J91" s="12"/>
       <c r="K91" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L91" s="12"/>
       <c r="M91" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N91" s="12"/>
     </row>
     <row r="92" spans="2:14">
-      <c r="B92" s="2" t="s">
-        <v>104</v>
+      <c r="B92" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D92" s="12"/>
       <c r="E92" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F92" s="12"/>
       <c r="G92" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H92" s="12"/>
       <c r="I92" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J92" s="12"/>
       <c r="K92" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N92" s="12"/>
     </row>
     <row r="93" spans="2:14">
-      <c r="B93" s="4" t="s">
-        <v>105</v>
+      <c r="B93" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D93" s="12"/>
       <c r="E93" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F93" s="12"/>
       <c r="G93" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J93" s="12"/>
       <c r="K93" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L93" s="12"/>
       <c r="M93" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N93" s="12"/>
     </row>
     <row r="94" spans="2:14">
-      <c r="B94" s="5" t="s">
-        <v>106</v>
+      <c r="B94" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F94" s="12"/>
       <c r="G94" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J94" s="12"/>
       <c r="K94" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L94" s="12"/>
       <c r="M94" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N94" s="12"/>
     </row>
     <row r="95" spans="2:14">
-      <c r="B95" s="1" t="s">
-        <v>107</v>
+      <c r="B95" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F95" s="12"/>
       <c r="G95" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H95" s="12"/>
       <c r="I95" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J95" s="12"/>
       <c r="K95" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N95" s="12"/>
     </row>
     <row r="96" spans="2:14">
-      <c r="B96" s="2" t="s">
-        <v>108</v>
+      <c r="B96" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F96" s="12"/>
       <c r="G96" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H96" s="12"/>
       <c r="I96" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J96" s="12"/>
       <c r="K96" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L96" s="12"/>
       <c r="M96" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N96" s="12"/>
     </row>
     <row r="97" spans="2:14">
-      <c r="B97" s="1" t="s">
-        <v>109</v>
+      <c r="B97" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F97" s="12"/>
       <c r="G97" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H97" s="12"/>
       <c r="I97" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J97" s="12"/>
       <c r="K97" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L97" s="12"/>
       <c r="M97" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N97" s="12"/>
     </row>
     <row r="98" spans="2:14">
-      <c r="B98" s="2" t="s">
-        <v>110</v>
+      <c r="B98" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F98" s="12"/>
       <c r="G98" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H98" s="12"/>
       <c r="I98" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J98" s="12"/>
       <c r="K98" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L98" s="12"/>
       <c r="M98" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N98" s="12"/>
     </row>
     <row r="99" spans="2:14">
-      <c r="B99" s="1" t="s">
-        <v>111</v>
+      <c r="B99" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D99" s="12"/>
       <c r="E99" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F99" s="12"/>
       <c r="G99" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J99" s="12"/>
       <c r="K99" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L99" s="12"/>
       <c r="M99" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N99" s="12"/>
     </row>
     <row r="100" spans="2:14">
-      <c r="B100" s="5" t="s">
-        <v>112</v>
+      <c r="B100" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F100" s="12"/>
       <c r="G100" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H100" s="12"/>
       <c r="I100" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J100" s="12"/>
       <c r="K100" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L100" s="12"/>
       <c r="M100" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N100" s="12"/>
     </row>
     <row r="101" spans="2:14">
-      <c r="B101" s="1" t="s">
-        <v>113</v>
+      <c r="B101" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F101" s="12"/>
       <c r="G101" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H101" s="12"/>
       <c r="I101" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J101" s="12"/>
       <c r="K101" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L101" s="12"/>
       <c r="M101" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N101" s="12"/>
     </row>
     <row r="102" spans="2:14">
-      <c r="B102" s="2" t="s">
-        <v>114</v>
+      <c r="B102" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F102" s="12"/>
       <c r="G102" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H102" s="12"/>
       <c r="I102" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L102" s="12"/>
       <c r="M102" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N102" s="12"/>
     </row>
     <row r="103" spans="2:14">
-      <c r="B103" s="1" t="s">
-        <v>115</v>
+      <c r="B103" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D103" s="12"/>
       <c r="E103" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F103" s="12"/>
       <c r="G103" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J103" s="12"/>
       <c r="K103" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L103" s="12"/>
       <c r="M103" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N103" s="12"/>
     </row>
     <row r="104" spans="2:14">
-      <c r="B104" s="2" t="s">
-        <v>116</v>
+      <c r="B104" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D104" s="12"/>
       <c r="E104" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F104" s="12"/>
       <c r="G104" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J104" s="12"/>
       <c r="K104" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L104" s="12"/>
       <c r="M104" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N104" s="12"/>
     </row>
     <row r="105" spans="2:14">
-      <c r="B105" s="1" t="s">
-        <v>117</v>
+      <c r="B105" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D105" s="12"/>
       <c r="E105" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F105" s="12"/>
       <c r="G105" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J105" s="12"/>
       <c r="K105" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N105" s="12"/>
     </row>
     <row r="106" spans="2:14">
-      <c r="B106" s="2" t="s">
-        <v>118</v>
+      <c r="B106" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D106" s="12"/>
       <c r="E106" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F106" s="12"/>
       <c r="G106" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J106" s="12"/>
       <c r="K106" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L106" s="12"/>
       <c r="M106" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N106" s="12"/>
     </row>
     <row r="107" spans="2:14">
-      <c r="B107" s="1" t="s">
-        <v>119</v>
+      <c r="B107" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F107" s="12"/>
       <c r="G107" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J107" s="12"/>
       <c r="K107" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N107" s="12"/>
     </row>
     <row r="108" spans="2:14">
-      <c r="B108" s="2" t="s">
-        <v>120</v>
+      <c r="B108" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F108" s="12"/>
       <c r="G108" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J108" s="12"/>
       <c r="K108" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L108" s="12"/>
       <c r="M108" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N108" s="12"/>
     </row>
     <row r="109" spans="2:14">
       <c r="B109" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F109" s="12"/>
       <c r="G109" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J109" s="12"/>
       <c r="K109" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L109" s="12"/>
       <c r="M109" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N109" s="12"/>
     </row>
     <row r="110" spans="2:14">
-      <c r="B110" s="8" t="s">
-        <v>122</v>
+      <c r="B110" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D110" s="12"/>
       <c r="E110" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F110" s="12"/>
       <c r="G110" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J110" s="12"/>
       <c r="K110" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N110" s="12"/>
     </row>
     <row r="111" spans="2:14">
-      <c r="B111" s="9" t="s">
-        <v>123</v>
+      <c r="B111" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F111" s="12"/>
       <c r="G111" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J111" s="12"/>
       <c r="K111" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L111" s="12"/>
       <c r="M111" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N111" s="12"/>
     </row>
     <row r="112" spans="2:14">
-      <c r="B112" s="3" t="s">
-        <v>124</v>
+      <c r="B112" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J112" s="12"/>
       <c r="K112" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L112" s="12"/>
       <c r="M112" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N112" s="12"/>
     </row>
     <row r="113" spans="2:14">
-      <c r="B113" s="3" t="s">
-        <v>125</v>
+      <c r="B113" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F113" s="12"/>
       <c r="G113" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J113" s="12"/>
       <c r="K113" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N113" s="12"/>
     </row>
     <row r="114" spans="2:14">
-      <c r="B114" s="3" t="s">
-        <v>126</v>
+      <c r="B114" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D114" s="12"/>
       <c r="E114" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F114" s="12"/>
       <c r="G114" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J114" s="12"/>
       <c r="K114" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L114" s="12"/>
       <c r="M114" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N114" s="12"/>
     </row>
     <row r="115" spans="2:14">
       <c r="B115" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F115" s="12"/>
       <c r="G115" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J115" s="12"/>
       <c r="K115" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L115" s="12"/>
       <c r="M115" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N115" s="12"/>
     </row>
     <row r="116" spans="2:14">
       <c r="B116" s="3" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F116" s="12"/>
       <c r="G116" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="J116" s="12"/>
       <c r="K116" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="L116" s="12"/>
       <c r="M116" s="10" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="N116" s="12"/>
     </row>
     <row r="117" spans="2:14">
       <c r="B117" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D117" s="13"/>
+        <v>128</v>
+      </c>
+      <c r="D117" s="12"/>
       <c r="E117" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" s="13"/>
+        <v>128</v>
+      </c>
+      <c r="F117" s="12"/>
       <c r="G117" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H117" s="13"/>
+        <v>128</v>
+      </c>
+      <c r="H117" s="12"/>
       <c r="I117" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J117" s="13"/>
+        <v>128</v>
+      </c>
+      <c r="J117" s="12"/>
       <c r="K117" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L117" s="13"/>
+        <v>128</v>
+      </c>
+      <c r="L117" s="12"/>
       <c r="M117" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N117" s="13"/>
-    </row>
-    <row r="118" spans="2:14" ht="14.25"/>
-    <row r="119" spans="2:14" ht="14.25"/>
-    <row r="120" spans="2:14" ht="14.25"/>
+        <v>128</v>
+      </c>
+      <c r="N117" s="12"/>
+    </row>
+    <row r="118" spans="2:14">
+      <c r="B118" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D118" s="12"/>
+      <c r="E118" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F118" s="12"/>
+      <c r="G118" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H118" s="12"/>
+      <c r="I118" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J118" s="12"/>
+      <c r="K118" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L118" s="12"/>
+      <c r="M118" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="N118" s="12"/>
+    </row>
+    <row r="119" spans="2:14">
+      <c r="B119" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D119" s="12"/>
+      <c r="E119" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F119" s="12"/>
+      <c r="G119" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H119" s="12"/>
+      <c r="I119" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J119" s="12"/>
+      <c r="K119" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L119" s="12"/>
+      <c r="M119" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="N119" s="12"/>
+    </row>
+    <row r="120" spans="2:14">
+      <c r="B120" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D120" s="13"/>
+      <c r="E120" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F120" s="13"/>
+      <c r="G120" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H120" s="13"/>
+      <c r="I120" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J120" s="13"/>
+      <c r="K120" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L120" s="13"/>
+      <c r="M120" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="N120" s="13"/>
+    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G117 I3:I117 K3:K117 C3:C117 E3:E117 M3:M117" xr:uid="{EED3058D-8EE4-4C50-9B07-06B10E3DD8DB}">
+  <conditionalFormatting sqref="C3:C120">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="equal">
+      <formula>"Si"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E120">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
+      <formula>"Si"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G120">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+      <formula>"Si"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I120">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+      <formula>"Si"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K120">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"Si"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M120">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Si"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G120 I3:I120 K3:K120 C3:C120 E3:E120 M3:M120" xr:uid="{EED3058D-8EE4-4C50-9B07-06B10E3DD8DB}">
       <formula1>$Q$3:$Q$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4850,338 +5143,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101007E6F4AFE9A8B4449B5095C950A419D4D" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="afa6857a8fdc9fcf49aef38709ae2c38">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="64a5dda8-8b4a-44a6-9503-2197c7d172f4" xmlns:ns3="e7c47c40-fd94-44e2-807b-aa57d1cb4f71" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2b715e5d13c8af849bd03d3024a4f124" ns2:_="" ns3:_="">
-    <xsd:import namespace="64a5dda8-8b4a-44a6-9503-2197c7d172f4"/>
-    <xsd:import namespace="e7c47c40-fd94-44e2-807b-aa57d1cb4f71"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:Fecha" minOccurs="0"/>
-                <xsd:element ref="ns2:Grupo" minOccurs="0"/>
-                <xsd:element ref="ns2:Fechamodificaci_x00f3_n" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="64a5dda8-8b4a-44a6-9503-2197c7d172f4" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="19" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="20" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9edf088c-3f8a-459d-848d-4665e1a51e2e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Fecha" ma:index="27" nillable="true" ma:displayName="Fecha" ma:format="DateOnly" ma:internalName="Fecha">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Grupo" ma:index="28" nillable="true" ma:displayName="Grupo" ma:format="Dropdown" ma:list="UserInfo" ma:SharePointGroup="0" ma:internalName="Grupo">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:User">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="Fechamodificaci_x00f3_n" ma:index="29" nillable="true" ma:displayName="Fecha modificación" ma:format="DateOnly" ma:internalName="Fechamodificaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e7c47c40-fd94-44e2-807b-aa57d1cb4f71" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a37b74d7-22fd-4a6c-96a7-4632356ed634}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e7c47c40-fd94-44e2-807b-aa57d1cb4f71">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Fechamodificaci_x00f3_n xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e7c47c40-fd94-44e2-807b-aa57d1cb4f71" xsi:nil="true"/>
-    <Fecha xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4" xsi:nil="true"/>
-    <Grupo xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Grupo>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="64a5dda8-8b4a-44a6-9503-2197c7d172f4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8946A969-D939-4330-8A8E-554BA21E5624}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{187F26EF-178D-4B87-96D7-096ED7328CD1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{641C4330-7E61-4DB2-A773-8A186DF3964E}"/>
 </file>